--- a/forms/trg/Formulir_TRG_livagri.xlsx
+++ b/forms/trg/Formulir_TRG_livagri.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B22)</f>
+        <f>COUNTA(Anggota!B5:B23)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F22)</f>
+        <f>COUNTA(Anggota!F5:F23)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,37 +913,33 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Ir. Lellah Rahim, M.Sc, IPU., ASEAN Eng.</t>
+          <t>Prof. Dr. Ir. Hastang, M.Si., IPU</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Leader</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t>Faculty of Animal Science, Hasanuddin University</t>
+          <t>Faculty of Animal Science Hasanuddin University</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Livestock Breeding, Quantitative Genetics</t>
+          <t>Livestock Economy</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
       <c r="H5" s="12" t="n"/>
       <c r="I5" s="12" t="n"/>
-      <c r="J5" s="11" t="inlineStr">
-        <is>
-          <t>0000-0001-7081-7786</t>
-        </is>
-      </c>
+      <c r="J5" s="12" t="n"/>
       <c r="K5" s="12" t="n"/>
       <c r="L5" s="11" t="inlineStr">
         <is>
-          <t>57190662046</t>
+          <t>55969421400</t>
         </is>
       </c>
       <c r="M5" s="11" t="inlineStr">
@@ -958,22 +954,22 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Emely J. Escala</t>
+          <t>Prof. Dr. Ir. Lellah Rahim, M.Sc, IPU., ASEAN Eng.</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>Capiz State University</t>
+          <t>Faculty of Animal Science, Hasanuddin University</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Animal Science - Animal Nutrition</t>
+          <t>Livestock Breeding, Quantitative Genetics</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
@@ -982,11 +978,15 @@
       <c r="I6" s="12" t="n"/>
       <c r="J6" s="11" t="inlineStr">
         <is>
-          <t>0000-0003-2666-9901</t>
+          <t>0000-0001-7081-7786</t>
         </is>
       </c>
       <c r="K6" s="12" t="n"/>
-      <c r="L6" s="12" t="n"/>
+      <c r="L6" s="11" t="inlineStr">
+        <is>
+          <t>57190662046</t>
+        </is>
+      </c>
       <c r="M6" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -999,22 +999,22 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Ir. Sitti Nurani Sirajuddin, S.Pt., M.Si., IPU., ASEAN Eng</t>
+          <t>Emely J. Escala</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>Faculty of Animal Science Hasanuddin University</t>
+          <t>Capiz State University</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Livestock Institutions</t>
+          <t>Animal Science - Animal Nutrition</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
@@ -1023,15 +1023,11 @@
       <c r="I7" s="12" t="n"/>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-3875-3185</t>
+          <t>0000-0003-2666-9901</t>
         </is>
       </c>
       <c r="K7" s="12" t="n"/>
-      <c r="L7" s="11" t="inlineStr">
-        <is>
-          <t>55969235700</t>
-        </is>
-      </c>
+      <c r="L7" s="12" t="n"/>
       <c r="M7" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1044,12 +1040,12 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Indrawirawan, S.Pt., M.Sc.</t>
+          <t>Prof. Dr. Ir. Sitti Nurani Sirajuddin, S.Pt., M.Si., IPU., ASEAN Eng</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -1059,7 +1055,7 @@
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Economic Production of Livestock</t>
+          <t>Livestock Institutions</t>
         </is>
       </c>
       <c r="F8" s="12" t="n"/>
@@ -1068,13 +1064,13 @@
       <c r="I8" s="12" t="n"/>
       <c r="J8" s="11" t="inlineStr">
         <is>
-          <t>0000-0003-2127-6092</t>
+          <t>0000-0002-3875-3185</t>
         </is>
       </c>
       <c r="K8" s="12" t="n"/>
       <c r="L8" s="11" t="inlineStr">
         <is>
-          <t>57208467652</t>
+          <t>55969235700</t>
         </is>
       </c>
       <c r="M8" s="11" t="inlineStr">
@@ -1089,22 +1085,22 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Heribertus Armaunut</t>
+          <t>Indrawirawan, S.Pt., M.Sc.</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>Doctoral Study Program of Animal Science, Faculty of Animal Science</t>
+          <t>Faculty of Animal Science Hasanuddin University</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Doctoral</t>
+          <t>Economic Production of Livestock</t>
         </is>
       </c>
       <c r="F9" s="12" t="n"/>
@@ -1113,13 +1109,13 @@
       <c r="I9" s="12" t="n"/>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>orcid-search/search?searchQuery=Heribertus%20Armaunut</t>
+          <t>0000-0003-2127-6092</t>
         </is>
       </c>
       <c r="K9" s="12" t="n"/>
       <c r="L9" s="11" t="inlineStr">
         <is>
-          <t>https://www.scopus.com/results/authorNamesList.uri?sort=count-f&amp;src=al&amp;sid=1f634be6913f58c5f2a479eec7963f51&amp;sot=al&amp;sdt=al&amp;sl=48&amp;s=AUTHLASTNAME%28Armaunut%29+AND+AUTHFIRST%28Heribertus%29&amp;st1=Armaunut&amp;st2=Heribertus&amp;orcidId=&amp;selectionPageSearch=anl&amp;reselectAuthor=false&amp;activeFlag=true&amp;showDocument=false&amp;resultsPerPage=20&amp;offset=1&amp;jtp=false&amp;currentPage=1&amp;previousSelectionCount=0&amp;tooManySelections=false&amp;previousResultCount=0&amp;authSubject=LFSC&amp;authSubject=HLSC&amp;authSubject=PHSC&amp;authSubject=SOSC&amp;exactAuthorSearch=false&amp;showFullList=false&amp;authorPreferredName=&amp;origin=searchauthorfreelookup&amp;affiliationId=&amp;txGid=3e69a2a4725858d6f59b990c5936ea6e</t>
+          <t>57208467652</t>
         </is>
       </c>
       <c r="M9" s="11" t="inlineStr">
@@ -1134,22 +1130,22 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Fauzan Adhima</t>
+          <t>Heribertus Armaunut</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>Magister</t>
+          <t>Doctoral Study Program of Animal Science, Faculty of Animal Science</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>LIVAGRI Team</t>
+          <t>Doctoral</t>
         </is>
       </c>
       <c r="F10" s="12" t="n"/>
@@ -1158,13 +1154,13 @@
       <c r="I10" s="12" t="n"/>
       <c r="J10" s="11" t="inlineStr">
         <is>
-          <t>orcid-search/search?searchQuery=Fauzan%20Adhima</t>
+          <t>orcid-search/search?searchQuery=Heribertus%20Armaunut</t>
         </is>
       </c>
       <c r="K10" s="12" t="n"/>
       <c r="L10" s="11" t="inlineStr">
         <is>
-          <t>https://www.scopus.com/results/authorNamesList.uri?sort=count-f&amp;src=al&amp;sid=da42e4f275ade27aa5458c65490d904e&amp;sot=al&amp;sdt=al&amp;sl=42&amp;s=AUTHLASTNAME%28Adhima%29+AND+AUTHFIRST%28Fauzan%29&amp;st1=Adhima&amp;st2=Fauzan&amp;orcidId=&amp;selectionPageSearch=anl&amp;reselectAuthor=false&amp;activeFlag=true&amp;showDocument=false&amp;resultsPerPage=20&amp;offset=1&amp;jtp=false&amp;currentPage=1&amp;previousSelectionCount=0&amp;tooManySelections=false&amp;previousResultCount=0&amp;authSubject=LFSC&amp;authSubject=HLSC&amp;authSubject=PHSC&amp;authSubject=SOSC&amp;exactAuthorSearch=false&amp;showFullList=false&amp;authorPreferredName=&amp;origin=searchauthorfreelookup&amp;affiliationId=&amp;txGid=d1d4d8e04305fdc63530f579c6ba5414</t>
+          <t>https://www.scopus.com/results/authorNamesList.uri?sort=count-f&amp;src=al&amp;sid=1f634be6913f58c5f2a479eec7963f51&amp;sot=al&amp;sdt=al&amp;sl=48&amp;s=AUTHLASTNAME%28Armaunut%29+AND+AUTHFIRST%28Heribertus%29&amp;st1=Armaunut&amp;st2=Heribertus&amp;orcidId=&amp;selectionPageSearch=anl&amp;reselectAuthor=false&amp;activeFlag=true&amp;showDocument=false&amp;resultsPerPage=20&amp;offset=1&amp;jtp=false&amp;currentPage=1&amp;previousSelectionCount=0&amp;tooManySelections=false&amp;previousResultCount=0&amp;authSubject=LFSC&amp;authSubject=HLSC&amp;authSubject=PHSC&amp;authSubject=SOSC&amp;exactAuthorSearch=false&amp;showFullList=false&amp;authorPreferredName=&amp;origin=searchauthorfreelookup&amp;affiliationId=&amp;txGid=3e69a2a4725858d6f59b990c5936ea6e</t>
         </is>
       </c>
       <c r="M10" s="11" t="inlineStr">
@@ -1177,18 +1173,46 @@
       <c r="A11" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="12" t="n"/>
-      <c r="C11" s="12" t="n"/>
-      <c r="D11" s="12" t="n"/>
-      <c r="E11" s="11" t="n"/>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>Fauzan Adhima</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>Magister</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>LIVAGRI Team</t>
+        </is>
+      </c>
       <c r="F11" s="12" t="n"/>
       <c r="G11" s="12" t="n"/>
       <c r="H11" s="12" t="n"/>
       <c r="I11" s="12" t="n"/>
-      <c r="J11" s="12" t="n"/>
+      <c r="J11" s="11" t="inlineStr">
+        <is>
+          <t>orcid-search/search?searchQuery=Fauzan%20Adhima</t>
+        </is>
+      </c>
       <c r="K11" s="12" t="n"/>
-      <c r="L11" s="12" t="n"/>
-      <c r="M11" s="12" t="n"/>
+      <c r="L11" s="11" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/results/authorNamesList.uri?sort=count-f&amp;src=al&amp;sid=da42e4f275ade27aa5458c65490d904e&amp;sot=al&amp;sdt=al&amp;sl=42&amp;s=AUTHLASTNAME%28Adhima%29+AND+AUTHFIRST%28Fauzan%29&amp;st1=Adhima&amp;st2=Fauzan&amp;orcidId=&amp;selectionPageSearch=anl&amp;reselectAuthor=false&amp;activeFlag=true&amp;showDocument=false&amp;resultsPerPage=20&amp;offset=1&amp;jtp=false&amp;currentPage=1&amp;previousSelectionCount=0&amp;tooManySelections=false&amp;previousResultCount=0&amp;authSubject=LFSC&amp;authSubject=HLSC&amp;authSubject=PHSC&amp;authSubject=SOSC&amp;exactAuthorSearch=false&amp;showFullList=false&amp;authorPreferredName=&amp;origin=searchauthorfreelookup&amp;affiliationId=&amp;txGid=d1d4d8e04305fdc63530f579c6ba5414</t>
+        </is>
+      </c>
+      <c r="M11" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -1377,15 +1401,32 @@
       <c r="L22" s="12" t="n"/>
       <c r="M22" s="12" t="n"/>
     </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="12" t="n"/>
+      <c r="C23" s="12" t="n"/>
+      <c r="D23" s="12" t="n"/>
+      <c r="E23" s="11" t="n"/>
+      <c r="F23" s="12" t="n"/>
+      <c r="G23" s="12" t="n"/>
+      <c r="H23" s="12" t="n"/>
+      <c r="I23" s="12" t="n"/>
+      <c r="J23" s="12" t="n"/>
+      <c r="K23" s="12" t="n"/>
+      <c r="L23" s="12" t="n"/>
+      <c r="M23" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
